--- a/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:36:35+00:00</t>
+    <t>2026-07-30T15:22:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:22:14+00:00</t>
+    <t>2026-07-31T08:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T08:51:02+00:00</t>
+    <t>2026-07-31T12:16:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:16:37+00:00</t>
+    <t>2026-07-31T12:21:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$37</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="272">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:21:47+00:00</t>
+    <t>2026-07-31T12:58:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -270,7 +270,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}onko-enlist-1:Eine EnLiST-Liniennummer (enlist-linenumber) darf nur vorliegen, wenn der Zählstatus (enlist-countable) 'counted' ist. {extension.where(url = 'https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/enlist-linenumber').exists() implies extension.where(url = 'https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/enlist-countable').value.ofType(CodeableConcept).coding.where(code = 'counted').exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -484,6 +484,38 @@
   </si>
   <si>
     <t>Referenz auf Medikationsverordnungen, die den Anlass für diese Therapielinie bilden – Ergänzung zu referralRequest, das auf ServiceRequest beschränkt ist.</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.extension:lineNumber</t>
+  </si>
+  <si>
+    <t>lineNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/enlist-linenumber}
+</t>
+  </si>
+  <si>
+    <t>EnLiST-Liniennummer</t>
+  </si>
+  <si>
+    <t>Nummer der systemischen Therapielinie nach EnLiST — nur für Linien, die in die LoT-Zählung eingehen.</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.extension:countable</t>
+  </si>
+  <si>
+    <t>countable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/enlist-countable}
+</t>
+  </si>
+  <si>
+    <t>EnLiST-Zählstatus</t>
+  </si>
+  <si>
+    <t>Zählstatus nach EnLiST — counted, not-counted oder investigational / iLoT.</t>
   </si>
   <si>
     <t>EpisodeOfCare.modifierExtension</t>
@@ -1160,7 +1192,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM35"/>
+  <dimension ref="A1:AM37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.19921875" customWidth="true" bestFit="true"/>
@@ -2424,48 +2456,46 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="D12" t="s" s="2">
-        <v>151</v>
+        <v>79</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="O12" t="s" s="2">
-        <v>155</v>
-      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>79</v>
       </c>
@@ -2513,7 +2543,7 @@
         <v>79</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2522,7 +2552,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>79</v>
+        <v>144</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>138</v>
@@ -2531,20 +2561,22 @@
         <v>79</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="D13" t="s" s="2">
         <v>79</v>
       </c>
@@ -2553,10 +2585,10 @@
         <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>79</v>
@@ -2565,13 +2597,13 @@
         <v>79</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2622,7 +2654,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -2631,61 +2663,63 @@
         <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>79</v>
+        <v>144</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>161</v>
+        <v>79</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>79</v>
+        <v>161</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>88</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>10</v>
+        <v>162</v>
       </c>
       <c r="M14" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="N14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>79</v>
       </c>
@@ -2709,60 +2743,60 @@
         <v>79</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="AG14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" hidden="true">
+      <c r="A15" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="Z14" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>171</v>
-      </c>
       <c r="B15" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2776,7 +2810,7 @@
         <v>78</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>79</v>
@@ -2785,13 +2819,13 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2842,7 +2876,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -2857,21 +2891,21 @@
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="16" hidden="true">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2879,30 +2913,32 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>176</v>
+        <v>107</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>177</v>
+        <v>10</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>79</v>
@@ -2927,13 +2963,13 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>79</v>
+        <v>176</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>79</v>
+        <v>178</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>79</v>
@@ -2951,10 +2987,10 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>87</v>
@@ -2963,28 +2999,28 @@
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" hidden="true">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>151</v>
+        <v>79</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -2994,7 +3030,7 @@
         <v>78</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>79</v>
@@ -3003,17 +3039,15 @@
         <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>132</v>
+        <v>182</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -3062,7 +3096,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3074,13 +3108,13 @@
         <v>79</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>79</v>
@@ -3088,46 +3122,42 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>132</v>
+        <v>186</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>79</v>
       </c>
@@ -3175,25 +3205,25 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>79</v>
@@ -3201,21 +3231,21 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>79</v>
+        <v>161</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>79</v>
@@ -3227,15 +3257,17 @@
         <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -3260,13 +3292,13 @@
         <v>79</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>167</v>
+        <v>79</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>79</v>
@@ -3284,25 +3316,25 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
@@ -3310,42 +3342,46 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>79</v>
+        <v>195</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
       </c>
@@ -3393,36 +3429,36 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3430,32 +3466,30 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>197</v>
+        <v>107</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -3480,11 +3514,13 @@
         <v>79</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="Y21" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="Z21" t="s" s="2">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>79</v>
@@ -3502,13 +3538,13 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>79</v>
@@ -3517,21 +3553,21 @@
         <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>203</v>
+        <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3542,25 +3578,25 @@
         <v>87</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3611,13 +3647,13 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>79</v>
@@ -3635,12 +3671,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3651,27 +3687,29 @@
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>176</v>
+        <v>207</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>79</v>
@@ -3696,13 +3734,11 @@
         <v>79</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>79</v>
+        <v>212</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>79</v>
@@ -3720,69 +3756,67 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>79</v>
+        <v>213</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" hidden="true">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>151</v>
+        <v>79</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>132</v>
+        <v>182</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -3831,7 +3865,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -3843,13 +3877,13 @@
         <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>79</v>
@@ -3857,46 +3891,42 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>132</v>
+        <v>186</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>79</v>
       </c>
@@ -3944,67 +3974,69 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>79</v>
+        <v>161</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>212</v>
+        <v>132</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -4053,68 +4085,72 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>215</v>
+        <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>79</v>
+        <v>195</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I27" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+      <c r="N27" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>79</v>
       </c>
@@ -4123,7 +4159,7 @@
         <v>79</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>79</v>
@@ -4138,13 +4174,13 @@
         <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>222</v>
+        <v>79</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>79</v>
@@ -4162,25 +4198,25 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
@@ -4188,10 +4224,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4199,7 +4235,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>87</v>
@@ -4214,13 +4250,13 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4271,10 +4307,10 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>87</v>
@@ -4286,13 +4322,13 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>79</v>
+        <v>225</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>79</v>
+        <v>226</v>
       </c>
     </row>
     <row r="29">
@@ -4323,13 +4359,13 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4341,7 +4377,7 @@
         <v>79</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>79</v>
+        <v>230</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>79</v>
@@ -4356,13 +4392,13 @@
         <v>79</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>79</v>
+        <v>231</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>79</v>
@@ -4383,7 +4419,7 @@
         <v>227</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>87</v>
@@ -4395,13 +4431,13 @@
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>231</v>
+        <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>232</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30">
@@ -4504,7 +4540,7 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>237</v>
+        <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>79</v>
@@ -4515,10 +4551,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4541,7 +4577,7 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>193</v>
+        <v>238</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>239</v>
@@ -4598,10 +4634,10 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>87</v>
@@ -4638,7 +4674,7 @@
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>88</v>
@@ -4647,7 +4683,7 @@
         <v>79</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>244</v>
@@ -4713,7 +4749,7 @@
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>79</v>
@@ -4744,7 +4780,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>87</v>
@@ -4756,16 +4792,16 @@
         <v>79</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4831,25 +4867,25 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>79</v>
+        <v>252</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>253</v>
+        <v>79</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -4925,7 +4961,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -4940,7 +4976,7 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>79</v>
@@ -4949,12 +4985,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4965,10 +5001,10 @@
         <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>79</v>
@@ -4977,17 +5013,15 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N35" t="s" s="2">
         <v>261</v>
       </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -5036,13 +5070,13 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>79</v>
@@ -5051,7 +5085,7 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>79</v>
+        <v>247</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>79</v>
@@ -5060,8 +5094,228 @@
         <v>79</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" hidden="true">
+      <c r="A37" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AM35">
+  <autoFilter ref="A1:AM37">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -5071,7 +5325,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI34">
+  <conditionalFormatting sqref="A2:AI36">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:58:15+00:00</t>
+    <t>2026-07-31T13:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -270,7 +270,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}onko-enlist-1:Eine EnLiST-Liniennummer (enlist-linenumber) darf nur vorliegen, wenn der Zählstatus (enlist-countable) 'counted' ist. {extension.where(url = 'https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/enlist-linenumber').exists() implies extension.where(url = 'https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/enlist-countable').value.ofType(CodeableConcept).coding.where(code = 'counted').exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}onko-enlist-1:Eine EnLiST-LoT-Designation (enlist-lot) darf nur vorliegen, wenn der Zählstatus (enlist-countable) 'counted' ist. {extension.where(url = 'https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/enlist-lot').exists() implies extension.where(url = 'https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/enlist-countable').value.ofType(CodeableConcept).coding.where(code = 'counted').exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -486,20 +486,20 @@
     <t>Referenz auf Medikationsverordnungen, die den Anlass für diese Therapielinie bilden – Ergänzung zu referralRequest, das auf ServiceRequest beschränkt ist.</t>
   </si>
   <si>
-    <t>EpisodeOfCare.extension:lineNumber</t>
-  </si>
-  <si>
-    <t>lineNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/enlist-linenumber}
+    <t>EpisodeOfCare.extension:lot</t>
+  </si>
+  <si>
+    <t>lot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/enlist-lot}
 </t>
   </si>
   <si>
-    <t>EnLiST-Liniennummer</t>
-  </si>
-  <si>
-    <t>Nummer der systemischen Therapielinie nach EnLiST — nur für Linien, die in die LoT-Zählung eingehen.</t>
+    <t>EnLiST-LoT-Designation</t>
+  </si>
+  <si>
+    <t>X.Y-Designation je Setting-Achse — eLoT, aLoT oder iLoT — nach EnLiST.</t>
   </si>
   <si>
     <t>EpisodeOfCare.extension:countable</t>
@@ -515,7 +515,7 @@
     <t>EnLiST-Zählstatus</t>
   </si>
   <si>
-    <t>Zählstatus nach EnLiST — counted, not-counted oder investigational / iLoT.</t>
+    <t>Zählstatus nach EnLiST — counted oder not-counted.</t>
   </si>
   <si>
     <t>EpisodeOfCare.modifierExtension</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:16:40+00:00</t>
+    <t>2026-07-31T13:26:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:26:52+00:00</t>
+    <t>2026-07-31T13:33:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:33:02+00:00</t>
+    <t>2026-07-31T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:38:59+00:00</t>
+    <t>2026-07-31T13:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$38</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="278">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:45:11+00:00</t>
+    <t>2026-07-31T14:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Eine onkologische Therapielinie (Line of Therapy, LoT) auf Basis von `EpisodeOfCare`, EnLiST-konform. Eine Therapielinie ist ein Behandlungsabschnitt mit einer bestimmten Intention und einer definierten Tumorerkrankung, der durch ein klinisches Ereignis (Progress, Toxizität, Patientenwunsch, Studienende, geplanter Wechsel) beendet wird. Die Verbindung zu einem `OnkoCarePlan` erfolgt über `CarePlan.encounter` → `Encounter.episodeOfCare` oder die Standard-Extension `workflow-episodeOfCare`.</t>
+    <t>Eine onkologische Therapielinie (Line of Therapy, LoT) auf Basis von `EpisodeOfCare`, EnLiST-konform. Eine Therapielinie ist ein **fachliches Kontinuum** mit definierter Intention und Tumorerkrankung, das durch ein klinisches Ereignis (Progress, Toxizität, Patientenwunsch, Studienende, geplanter Wechsel) beendet wird — und das organisatorisch in mehrere Episoden zerfallen kann, da `EpisodeOfCare` organisationsgebunden ist. Die EnLiST-Designation (`enlist-lot`) trägt je Linie **genau eine führende Episode** (main contributor); ausführende Einrichtungen dokumentieren eigene Episoden als Segmente (`enlist-line-segment`) mit gemeinsamer `lineId`. Bei gleichem Ort/Sektor fallen Führung und Ausführung in einer einzigen Episode zusammen. Die Verbindung zu einem `OnkoCarePlan` erfolgt über die Standard-Extension `workflow-episodeOfCare`.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -270,7 +270,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}onko-enlist-1:Eine EnLiST-LoT-Designation (enlist-lot) darf nur vorliegen, wenn der Zählstatus (enlist-countable) 'counted' ist. {extension.where(url = 'https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/enlist-lot').exists() implies extension.where(url = 'https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/enlist-countable').value.ofType(CodeableConcept).coding.where(code = 'counted').exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}onko-enlist-1:Eine EnLiST-LoT-Designation (enlist-lot) darf nur vorliegen, wenn der Zählstatus (enlist-countable) 'counted' ist. {extension.where(url = 'https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/enlist-lot').exists() implies extension.where(url = 'https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/enlist-countable').value.ofType(CodeableConcept).coding.where(code = 'counted').exists()}onko-enlist-3:Zählstatus 'counted' erfordert eine EnLiST-Designation (enlist-lot, führende Episode) oder einen Segment-Marker (enlist-line-segment, ausführende Episode). {extension.where(url = 'https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/enlist-countable').value.ofType(CodeableConcept).coding.where(code = 'counted').exists() implies (extension.where(url = 'https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/enlist-lot').exists() or extension.where(url = 'https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/enlist-line-segment').exists())}onko-enlist-4:enlist-lot (führende Episode) und enlist-line-segment (ausführendes Segment) dürfen nicht an derselben Episode vorliegen. {(extension.where(url = 'https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/enlist-lot').exists() and extension.where(url = 'https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/enlist-line-segment').exists()).not()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -500,6 +500,26 @@
   </si>
   <si>
     <t>X.Y-Designation je Setting-Achse — eLoT, aLoT oder iLoT — nach EnLiST.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}onko-enlist-2:Die notation (falls vorhanden) muss aus setting, line und modification zusammengesetzt sein (z. B. 'eLoT 1.0'). {extension.where(url = 'notation').exists() implies extension.where(url = 'notation').value = extension.where(url = 'setting').value.ofType(CodeableConcept).coding.first().code + ' ' + extension.where(url = 'line').value.toString() + '.' + extension.where(url = 'modification').value.toString()}</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.extension:lineSegment</t>
+  </si>
+  <si>
+    <t>lineSegment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/enlist-line-segment}
+</t>
+  </si>
+  <si>
+    <t>EnLiST-Linien-Segment</t>
+  </si>
+  <si>
+    <t>Segment-Marker einer ausführenden Einrichtung — gemeinsame lineId, keine eigene Designation.</t>
   </si>
   <si>
     <t>EpisodeOfCare.extension:countable</t>
@@ -1192,7 +1212,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM37"/>
+  <dimension ref="A1:AM38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.19921875" customWidth="true" bestFit="true"/>
@@ -2555,7 +2575,7 @@
         <v>144</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>79</v>
@@ -2569,13 +2589,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>131</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>79</v>
@@ -2597,13 +2617,13 @@
         <v>79</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2678,48 +2698,46 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="D14" t="s" s="2">
-        <v>161</v>
+        <v>79</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O14" t="s" s="2">
         <v>165</v>
       </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>79</v>
       </c>
@@ -2767,7 +2785,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -2776,7 +2794,7 @@
         <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>79</v>
+        <v>144</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>138</v>
@@ -2785,7 +2803,7 @@
         <v>79</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>79</v>
@@ -2793,14 +2811,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>79</v>
+        <v>167</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -2813,22 +2831,26 @@
         <v>79</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
+      <c r="O15" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>79</v>
       </c>
@@ -2876,7 +2898,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -2888,19 +2910,19 @@
         <v>79</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>171</v>
+        <v>79</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>173</v>
       </c>
@@ -2913,32 +2935,30 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>107</v>
+        <v>174</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>10</v>
+        <v>175</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>79</v>
@@ -2963,13 +2983,13 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>176</v>
+        <v>79</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>177</v>
+        <v>79</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>178</v>
+        <v>79</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>79</v>
@@ -2990,10 +3010,10 @@
         <v>173</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>79</v>
@@ -3002,21 +3022,21 @@
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3024,30 +3044,32 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>88</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>182</v>
+        <v>107</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>183</v>
+        <v>10</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -3072,13 +3094,13 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>79</v>
+        <v>182</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>79</v>
+        <v>183</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>79</v>
+        <v>184</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
@@ -3096,13 +3118,13 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>79</v>
@@ -3111,21 +3133,21 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" hidden="true">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3136,10 +3158,10 @@
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>79</v>
@@ -3148,13 +3170,13 @@
         <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3205,25 +3227,25 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>79</v>
@@ -3231,21 +3253,21 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>161</v>
+        <v>79</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>79</v>
@@ -3257,17 +3279,15 @@
         <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>132</v>
+        <v>192</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -3316,19 +3336,19 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>79</v>
@@ -3342,14 +3362,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3362,26 +3382,24 @@
         <v>79</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K20" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>79</v>
       </c>
@@ -3429,7 +3447,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3447,7 +3465,7 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -3455,42 +3473,46 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>79</v>
       </c>
@@ -3514,13 +3536,13 @@
         <v>79</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>176</v>
+        <v>79</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>177</v>
+        <v>79</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>178</v>
+        <v>79</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>79</v>
@@ -3538,25 +3560,25 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
@@ -3564,10 +3586,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3590,13 +3612,13 @@
         <v>79</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>203</v>
+        <v>107</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3623,13 +3645,13 @@
         <v>79</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>79</v>
+        <v>182</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>79</v>
+        <v>183</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>79</v>
+        <v>184</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>79</v>
@@ -3647,7 +3669,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>87</v>
@@ -3671,12 +3693,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3684,32 +3706,30 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>79</v>
@@ -3734,11 +3754,13 @@
         <v>79</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>212</v>
+        <v>79</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>79</v>
@@ -3756,13 +3778,13 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>79</v>
@@ -3771,21 +3793,21 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>213</v>
+        <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>214</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3793,7 +3815,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>78</v>
@@ -3808,15 +3830,17 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="M24" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -3841,13 +3865,11 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>79</v>
+        <v>218</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -3865,7 +3887,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -3880,21 +3902,21 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>79</v>
+        <v>219</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="25" hidden="true">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3902,28 +3924,28 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>187</v>
+        <v>222</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>188</v>
+        <v>223</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3974,25 +3996,25 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
@@ -4000,21 +4022,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>161</v>
+        <v>79</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>79</v>
@@ -4026,17 +4048,15 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>132</v>
+        <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -4085,19 +4105,19 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>79</v>
@@ -4111,14 +4131,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4131,26 +4151,24 @@
         <v>79</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>79</v>
       </c>
@@ -4198,7 +4216,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4216,50 +4234,54 @@
         <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I28" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>222</v>
+        <v>132</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
       </c>
@@ -4307,28 +4329,28 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>225</v>
+        <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>226</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29">
@@ -4359,13 +4381,13 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4377,7 +4399,7 @@
         <v>79</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>230</v>
+        <v>79</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>79</v>
@@ -4392,13 +4414,13 @@
         <v>79</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>231</v>
+        <v>79</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>232</v>
+        <v>79</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>79</v>
@@ -4419,7 +4441,7 @@
         <v>227</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>87</v>
@@ -4431,13 +4453,13 @@
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>79</v>
+        <v>231</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>79</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30">
@@ -4453,7 +4475,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>87</v>
@@ -4468,13 +4490,13 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4486,7 +4508,7 @@
         <v>79</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>79</v>
@@ -4501,13 +4523,13 @@
         <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>79</v>
+        <v>237</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>79</v>
+        <v>238</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>79</v>
@@ -4551,10 +4573,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4562,7 +4584,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>87</v>
@@ -4577,13 +4599,13 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4634,10 +4656,10 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>87</v>
@@ -4649,13 +4671,13 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>241</v>
+        <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>242</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32">
@@ -4671,7 +4693,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>87</v>
@@ -4746,7 +4768,7 @@
         <v>243</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>87</v>
@@ -4764,15 +4786,15 @@
         <v>79</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>79</v>
+        <v>248</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4780,7 +4802,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>87</v>
@@ -4795,13 +4817,13 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>203</v>
+        <v>250</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4852,7 +4874,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -4867,21 +4889,21 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>252</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4889,10 +4911,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>88</v>
@@ -4901,10 +4923,10 @@
         <v>79</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>254</v>
+        <v>209</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>255</v>
@@ -4961,13 +4983,13 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>79</v>
@@ -4982,15 +5004,15 @@
         <v>79</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>79</v>
+        <v>258</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5001,7 +5023,7 @@
         <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>88</v>
@@ -5013,13 +5035,13 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5070,13 +5092,13 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>79</v>
@@ -5085,7 +5107,7 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>79</v>
@@ -5096,21 +5118,21 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>263</v>
+        <v>79</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>88</v>
@@ -5122,13 +5144,13 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5179,13 +5201,13 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>79</v>
@@ -5194,7 +5216,7 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>79</v>
@@ -5203,16 +5225,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>79</v>
+        <v>269</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5222,7 +5244,7 @@
         <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>79</v>
@@ -5231,17 +5253,15 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -5290,7 +5310,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5305,7 +5325,7 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>79</v>
+        <v>253</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>79</v>
@@ -5314,8 +5334,119 @@
         <v>79</v>
       </c>
     </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AM37">
+  <autoFilter ref="A1:AM38">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -5325,7 +5456,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI36">
+  <conditionalFormatting sqref="A2:AI37">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:14:54+00:00</t>
+    <t>2026-07-31T14:25:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:25:45+00:00</t>
+    <t>2026-08-02T18:42:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:42:01+00:00</t>
+    <t>2026-08-02T18:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:51:55+00:00</t>
+    <t>2026-08-03T05:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
